--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-19 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-20 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -1514,10 +1514,10 @@
         <v>11.52</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>9.73</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.98</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="6">
@@ -1538,10 +1538,10 @@
         <v>35.316605</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>13.63</v>
+        <v>13.682</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.418</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="7">
@@ -1560,10 +1560,10 @@
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>5.759</v>
+        <v>5.683</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.712</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="8">
@@ -1584,10 +1584,10 @@
         <v>19.984375</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>12.577</v>
+        <v>12.691</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.411</v>
+        <v>2.432</v>
       </c>
     </row>
     <row r="9">
@@ -1608,10 +1608,10 @@
         <v>18.618422</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>7.94</v>
+        <v>7.793</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.177</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="10">
@@ -1650,10 +1650,10 @@
         <v>36.964912</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>26.019</v>
+        <v>24.976</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.887</v>
+        <v>1.812</v>
       </c>
     </row>
     <row r="12">
@@ -1672,10 +1672,10 @@
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>6.699</v>
+        <v>6.646</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.517</v>
+        <v>1.505</v>
       </c>
     </row>
     <row r="13">
@@ -1694,10 +1694,10 @@
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-326.939</v>
+        <v>-327.335</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>8.288</v>
+        <v>8.298</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-20 17:39 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-21 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.044509997</v>
+        <v>0.04450999999999999</v>
       </c>
     </row>
     <row r="6">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-21 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.719</v>
+        <v>0.71</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>102.39</v>
+        <v>110.55</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.823</v>
+        <v>0.795</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04450999999999999</v>
+        <v>0.04409999847412109</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>42276818.59556597</v>
+        <v>42276819.53867029</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>102.39</v>
+        <v>110.55</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>4328723456</v>
+        <v>4673702400</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>11.52</v>
+        <v>12.44</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>9.359999999999999</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>0.95</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>7502742528</v>
+        <v>7194332160</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>35.316605</v>
+        <v>33.864864</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>13.682</v>
+        <v>13.27</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.42</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="7">
@@ -1556,14 +1556,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1530001024</v>
+        <v>1306113280</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>5.683</v>
+        <v>5.69</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.703</v>
+        <v>0.704</v>
       </c>
     </row>
     <row r="8">
@@ -1578,16 +1578,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>3763702016</v>
+        <v>3801957120</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>19.984375</v>
+        <v>20.1875</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>12.691</v>
+        <v>12.767</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.432</v>
+        <v>2.447</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>6521582080</v>
+        <v>6268093440</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>18.618422</v>
+        <v>17.894737</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>7.793</v>
+        <v>7.63</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.174</v>
+        <v>0.171</v>
       </c>
     </row>
     <row r="10">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2443728896</v>
+        <v>2724108288</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>2650381312</v>
+        <v>3038441472</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>36.964912</v>
+        <v>42.377193</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>24.976</v>
+        <v>28.96</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>1.812</v>
+        <v>2.101</v>
       </c>
     </row>
     <row r="12">
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>350365664</v>
+        <v>381888224</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>6.646</v>
+        <v>6.722</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.505</v>
+        <v>1.522</v>
       </c>
     </row>
     <row r="13">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>7247755776</v>
+        <v>7232419328</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-327.335</v>
+        <v>-326.194</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>8.298</v>
+        <v>8.269</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-06-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.71</v>
+        <v>0.715</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>110.55</v>
+        <v>106.31</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>0.795</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04409999847412109</v>
+        <v>0.04467000007629394</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>42276819.53867029</v>
+        <v>42276819.11391214</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>110.55</v>
+        <v>106.31</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>4673702400</v>
+        <v>4494448640</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>12.44</v>
+        <v>11.94</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>9.960000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>1.01</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>7194332160</v>
+        <v>7233703936</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>33.864864</v>
+        <v>34.050194</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>13.27</v>
+        <v>13.398</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.407</v>
+        <v>0.411</v>
       </c>
     </row>
     <row r="7">
@@ -1556,14 +1556,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>1306113280</v>
+        <v>1511228288</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>5.69</v>
+        <v>4.928</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>0.704</v>
+        <v>0.569</v>
       </c>
     </row>
     <row r="8">
@@ -1578,16 +1578,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>3801957120</v>
+        <v>4287148032</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>20.1875</v>
+        <v>22.76375</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>12.767</v>
+        <v>12.95</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.447</v>
+        <v>2.482</v>
       </c>
     </row>
     <row r="9">
@@ -1602,16 +1602,16 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>6268093440</v>
+        <v>6353357824</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>17.894737</v>
+        <v>18.138159</v>
       </c>
       <c r="E9" s="33" t="n">
-        <v>7.63</v>
+        <v>7.626</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>0.171</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="10">
@@ -1626,7 +1626,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>2724108288</v>
+        <v>2939558144</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n"/>
@@ -1644,16 +1644,16 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>3038441472</v>
+        <v>3228383488</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>42.377193</v>
+        <v>45.026318</v>
       </c>
       <c r="E11" s="33" t="n">
-        <v>28.96</v>
+        <v>29.163</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>2.101</v>
+        <v>2.115</v>
       </c>
     </row>
     <row r="12">
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>381888224</v>
+        <v>411860512</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>6.722</v>
+        <v>6.735</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>1.522</v>
+        <v>1.525</v>
       </c>
     </row>
     <row r="13">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>7232419328</v>
+        <v>7187564032</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-326.194</v>
+        <v>-325.448</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>8.269</v>
+        <v>8.25</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -20,11 +20,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="7">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="165" formatCode="+0.0%;-0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -126,21 +126,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -149,9 +150,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -595,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -620,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-01 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-07-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -640,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.715</v>
+        <v>0.822</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -656,7 +657,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -671,10 +672,8 @@
           <t>DCF intrinsic value / share</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B8" s="7" t="n">
+        <v>268.14</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -689,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>106.31</v>
+        <v>116.03</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,10 +702,8 @@
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="B10" s="8" t="n">
+        <v>1.311</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -729,8 +726,8 @@
           <t>value_score</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
-        <v>0.8100000000000001</v>
+      <c r="B13" s="9" t="n">
+        <v>0.777</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -740,7 +737,7 @@
           <t>comps_percentile</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="9" t="n">
         <v>0.667</v>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -749,52 +746,67 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>dcf_margin</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Normalized (intrinsic − market) / market, clipped ±50%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Honest caveats (read before acting)</t>
         </is>
       </c>
-      <c r="B16" s="3" t="n"/>
-      <c r="C16" s="3" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
-        </is>
-      </c>
+      <c r="B17" s="3" t="n"/>
+      <c r="C17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
+          <t>Lite DCF: 5y horizon, 70/30 equity/debt cap structure assumed, FCF growth from 3y trailing trend.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
+          <t>Peer set is FMP's algorithmic /stock-peers — may include weak comps for unusual business models.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
+          <t>Net cash treatment uses cashAndShortTermInvestments (operating cash); excludes LT marketable</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+          <t xml:space="preserve">  securities, which understates intrinsic for cash-rich companies like AAPL (~$80B in LT inv).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Margin of safety is normalized to 0..1; flip to the DCF tab for the raw % gap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>This is a SIGNAL screen, not an investment thesis. Verify with primary filings before acting.</t>
         </is>
@@ -804,6 +816,7 @@
   <mergeCells count="11">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A17:C17"/>
@@ -812,7 +825,6 @@
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -878,8 +890,8 @@
           <t>Risk-free rate (10y Treasury)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>0.04467000007629394</v>
+      <c r="B5" s="10" t="n">
+        <v>0.04654000282287598</v>
       </c>
     </row>
     <row r="6">
@@ -888,7 +900,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" s="10" t="n">
         <v>0.05</v>
       </c>
     </row>
@@ -898,7 +910,7 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -908,7 +920,7 @@
           <t>Credit spread over risk-free</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" s="10" t="n">
         <v>0.02</v>
       </c>
     </row>
@@ -918,7 +930,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" s="10" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -928,7 +940,7 @@
           <t>Equity weight (cap structure)</t>
         </is>
       </c>
-      <c r="B10" s="11" t="n">
+      <c r="B10" s="12" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -938,7 +950,7 @@
           <t>FCF growth (flat, faded avg)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="10" t="n">
         <v>0.0506380650537684</v>
       </c>
     </row>
@@ -948,7 +960,7 @@
           <t>Terminal growth rate</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="10" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -958,7 +970,7 @@
           <t>Latest FCF ($, base year)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="13" t="n">
         <v>577000000</v>
       </c>
     </row>
@@ -968,7 +980,7 @@
           <t>Cost of equity (CAPM)</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="14">
         <f>B5+B7*B6</f>
         <v/>
       </c>
@@ -979,18 +991,18 @@
           <t>After-tax cost of debt</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="14">
         <f>(B5+B8)*(1-B9)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="16">
         <f>B10*B15+(1-B10)*B16</f>
         <v/>
       </c>
@@ -1037,23 +1049,23 @@
           <t>Projected FCF</t>
         </is>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="17">
         <f>$B$13*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="C22" s="16">
+      <c r="C22" s="17">
         <f>B22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="D22" s="16">
+      <c r="D22" s="17">
         <f>C22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="E22" s="16">
+      <c r="E22" s="17">
         <f>D22*(1+$B$11)</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="17">
         <f>E22*(1+$B$11)</f>
         <v/>
       </c>
@@ -1064,23 +1076,23 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B23" s="17">
+      <c r="B23" s="18">
         <f>1/(1+$B$17)^1</f>
         <v/>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="18">
         <f>1/(1+$B$17)^2</f>
         <v/>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="18">
         <f>1/(1+$B$17)^3</f>
         <v/>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="18">
         <f>1/(1+$B$17)^4</f>
         <v/>
       </c>
-      <c r="F23" s="17">
+      <c r="F23" s="18">
         <f>1/(1+$B$17)^5</f>
         <v/>
       </c>
@@ -1091,23 +1103,23 @@
           <t>PV of FCF</t>
         </is>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="17">
         <f>B22*B23</f>
         <v/>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="17">
         <f>C22*C23</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <f>D22*D23</f>
         <v/>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <f>E22*E23</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="17">
         <f>F22*F23</f>
         <v/>
       </c>
@@ -1118,7 +1130,7 @@
           <t>Sum of PV (explicit 5y)</t>
         </is>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="17">
         <f>SUM(B24:F24)</f>
         <v/>
       </c>
@@ -1129,7 +1141,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="17">
         <f>F22*(1+B12)/(B17-B12)</f>
         <v/>
       </c>
@@ -1140,18 +1152,18 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B27/(1+B17)^5</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B29" s="19">
+      <c r="B29" s="20">
         <f>B26+B28</f>
         <v/>
       </c>
@@ -1176,7 +1188,7 @@
           <t>Less: total debt</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n">
+      <c r="B32" s="13" t="n">
         <v>2675000064</v>
       </c>
     </row>
@@ -1186,7 +1198,7 @@
           <t>Plus: cash &amp; ST investments</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n">
+      <c r="B33" s="13" t="n">
         <v>109000000</v>
       </c>
     </row>
@@ -1196,7 +1208,7 @@
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="17">
         <f>B29-B32+B33</f>
         <v/>
       </c>
@@ -1207,17 +1219,17 @@
           <t>Diluted shares outstanding</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>42276819.11391214</v>
+      <c r="B35" s="21" t="n">
+        <v>42276819.16745669</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Intrinsic per share</t>
         </is>
       </c>
-      <c r="B36" s="21">
+      <c r="B36" s="22">
         <f>B34/B35</f>
         <v/>
       </c>
@@ -1228,17 +1240,17 @@
           <t>Current market price</t>
         </is>
       </c>
-      <c r="B37" s="22" t="n">
-        <v>106.31</v>
+      <c r="B37" s="23" t="n">
+        <v>116.03</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Margin of safety</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="24">
         <f>(B36-B37)/B37</f>
         <v/>
       </c>
@@ -1258,158 +1270,158 @@
       <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="inlineStr">
+      <c r="A42" s="25" t="inlineStr">
         <is>
           <t>WACC ↓ / TermG →</t>
         </is>
       </c>
-      <c r="B42" s="25">
+      <c r="B42" s="26">
         <f>$B$12+-0.01</f>
         <v/>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="26">
         <f>$B$12+-0.005</f>
         <v/>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="26">
         <f>$B$12+0.0</f>
         <v/>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="26">
         <f>$B$12+0.005</f>
         <v/>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="26">
         <f>$B$12+0.01</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="25">
+      <c r="A43" s="26">
         <f>$B$17+-0.01</f>
         <v/>
       </c>
-      <c r="B43" s="26">
+      <c r="B43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A43-B$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C43" s="26">
+      <c r="C43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A43-C$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D43" s="26">
+      <c r="D43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A43-D$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A43-E$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A43)^1+$B$13*(1+$B$11)^2/(1+A43)^2+$B$13*(1+$B$11)^3/(1+A43)^3+$B$13*(1+$B$11)^4/(1+A43)^4+$B$13*(1+$B$11)^5/(1+A43)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A43-F$42))/(1+A43)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="25">
+      <c r="A44" s="26">
         <f>$B$17+-0.005</f>
         <v/>
       </c>
-      <c r="B44" s="26">
+      <c r="B44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A44-B$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C44" s="26">
+      <c r="C44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A44-C$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D44" s="26">
+      <c r="D44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A44-D$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A44-E$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A44)^1+$B$13*(1+$B$11)^2/(1+A44)^2+$B$13*(1+$B$11)^3/(1+A44)^3+$B$13*(1+$B$11)^4/(1+A44)^4+$B$13*(1+$B$11)^5/(1+A44)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A44-F$42))/(1+A44)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="25">
+      <c r="A45" s="26">
         <f>$B$17+0.0</f>
         <v/>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A45-B$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C45" s="26">
+      <c r="C45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A45-C$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D45" s="27">
+      <c r="D45" s="28">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A45-D$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A45-E$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F45" s="26">
+      <c r="F45" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A45)^1+$B$13*(1+$B$11)^2/(1+A45)^2+$B$13*(1+$B$11)^3/(1+A45)^3+$B$13*(1+$B$11)^4/(1+A45)^4+$B$13*(1+$B$11)^5/(1+A45)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A45-F$42))/(1+A45)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="25">
+      <c r="A46" s="26">
         <f>$B$17+0.005</f>
         <v/>
       </c>
-      <c r="B46" s="26">
+      <c r="B46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A46-B$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C46" s="26">
+      <c r="C46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A46-C$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D46" s="26">
+      <c r="D46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A46-D$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A46-E$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F46" s="26">
+      <c r="F46" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A46)^1+$B$13*(1+$B$11)^2/(1+A46)^2+$B$13*(1+$B$11)^3/(1+A46)^3+$B$13*(1+$B$11)^4/(1+A46)^4+$B$13*(1+$B$11)^5/(1+A46)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A46-F$42))/(1+A46)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="25">
+      <c r="A47" s="26">
         <f>$B$17+0.01</f>
         <v/>
       </c>
-      <c r="B47" s="26">
+      <c r="B47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+B$42)/(A47-B$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="C47" s="26">
+      <c r="C47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+C$42)/(A47-C$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="D47" s="26">
+      <c r="D47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+D$42)/(A47-D$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+E$42)/(A47-E$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
-      <c r="F47" s="26">
+      <c r="F47" s="27">
         <f>($B$13*(1+$B$11)^1/(1+A47)^1+$B$13*(1+$B$11)^2/(1+A47)^2+$B$13*(1+$B$11)^3/(1+A47)^3+$B$13*(1+$B$11)^4/(1+A47)^4+$B$13*(1+$B$11)^5/(1+A47)^5+($B$13*(1+$B$11)^5*(1+F$42)/(A47-F$42))/(1+A47)^5-$B$32+$B$33)/$B$35</f>
         <v/>
       </c>
@@ -1434,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1465,59 +1477,59 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="29" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="29" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C4" s="28" t="inlineStr">
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="D4" s="28" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>P/E (TTM)</t>
         </is>
       </c>
-      <c r="E4" s="28" t="inlineStr">
+      <c r="E4" s="29" t="inlineStr">
         <is>
           <t>EV/EBITDA</t>
         </is>
       </c>
-      <c r="F4" s="28" t="inlineStr">
+      <c r="F4" s="29" t="inlineStr">
         <is>
           <t>EV/Revenue</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>SAIC</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>Science Applications International Corporation</t>
         </is>
       </c>
-      <c r="C5" s="30" t="n">
-        <v>4494448640</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <v>11.94</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <v>9.81</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <v>0.99</v>
+      <c r="C5" s="31" t="n">
+        <v>4905379328</v>
+      </c>
+      <c r="D5" s="32" t="n">
+        <v>13.05</v>
+      </c>
+      <c r="E5" s="32" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="F5" s="32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1531,17 +1543,17 @@
           <t>Avnet, Inc.</t>
         </is>
       </c>
-      <c r="C6" s="32" t="n">
-        <v>7233703936</v>
-      </c>
-      <c r="D6" s="33" t="n">
-        <v>34.050194</v>
-      </c>
-      <c r="E6" s="33" t="n">
-        <v>13.398</v>
-      </c>
-      <c r="F6" s="33" t="n">
-        <v>0.411</v>
+      <c r="C6" s="33" t="n">
+        <v>7414156288</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <v>34.899616</v>
+      </c>
+      <c r="E6" s="34" t="n">
+        <v>13.508</v>
+      </c>
+      <c r="F6" s="34" t="n">
+        <v>0.414</v>
       </c>
     </row>
     <row r="7">
@@ -1555,15 +1567,15 @@
           <t>Concentrix Corporation</t>
         </is>
       </c>
-      <c r="C7" s="32" t="n">
-        <v>1511228288</v>
-      </c>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n">
-        <v>4.928</v>
-      </c>
-      <c r="F7" s="33" t="n">
-        <v>0.569</v>
+      <c r="C7" s="33" t="n">
+        <v>1451626624</v>
+      </c>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n">
+        <v>5.257</v>
+      </c>
+      <c r="F7" s="34" t="n">
+        <v>0.67</v>
       </c>
     </row>
     <row r="8">
@@ -1577,17 +1589,17 @@
           <t>DLocal Limited</t>
         </is>
       </c>
-      <c r="C8" s="32" t="n">
-        <v>4287148032</v>
-      </c>
-      <c r="D8" s="33" t="n">
-        <v>22.76375</v>
-      </c>
-      <c r="E8" s="33" t="n">
-        <v>12.95</v>
-      </c>
-      <c r="F8" s="33" t="n">
-        <v>2.482</v>
+      <c r="C8" s="33" t="n">
+        <v>4209519872</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <v>22.351564</v>
+      </c>
+      <c r="E8" s="34" t="n">
+        <v>15.191</v>
+      </c>
+      <c r="F8" s="34" t="n">
+        <v>2.912</v>
       </c>
     </row>
     <row r="9">
@@ -1601,17 +1613,17 @@
           <t>Ingram Micro Holding Corporatio</t>
         </is>
       </c>
-      <c r="C9" s="32" t="n">
-        <v>6353357824</v>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>18.138159</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>7.626</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>0.17</v>
+      <c r="C9" s="33" t="n">
+        <v>6858031616</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <v>19.578947</v>
+      </c>
+      <c r="E9" s="34" t="n">
+        <v>8.012</v>
+      </c>
+      <c r="F9" s="34" t="n">
+        <v>0.179</v>
       </c>
     </row>
     <row r="10">
@@ -1625,12 +1637,12 @@
           <t>NIQ Global Intelligence plc</t>
         </is>
       </c>
-      <c r="C10" s="32" t="n">
-        <v>2939558144</v>
-      </c>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
+      <c r="C10" s="33" t="n">
+        <v>3140250880</v>
+      </c>
+      <c r="D10" s="34" t="n"/>
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1643,17 +1655,17 @@
           <t>Paymentus Holdings, Inc.</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>3228383488</v>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>45.026318</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>29.163</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>2.115</v>
+      <c r="C11" s="33" t="n">
+        <v>3649148672</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <v>50.894737</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>36.563</v>
+      </c>
+      <c r="F11" s="34" t="n">
+        <v>2.652</v>
       </c>
     </row>
     <row r="12">
@@ -1667,95 +1679,73 @@
           <t>Paysafe Limited</t>
         </is>
       </c>
-      <c r="C12" s="32" t="n">
-        <v>411860512</v>
-      </c>
-      <c r="D12" s="33" t="n"/>
-      <c r="E12" s="33" t="n">
-        <v>6.735</v>
-      </c>
-      <c r="F12" s="33" t="n">
-        <v>1.525</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SLAB</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Silicon Laboratories, Inc.</t>
-        </is>
-      </c>
-      <c r="C13" s="32" t="n">
-        <v>7187564032</v>
-      </c>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n">
-        <v>-325.448</v>
-      </c>
-      <c r="F13" s="33" t="n">
-        <v>8.25</v>
+      <c r="C12" s="33" t="n">
+        <v>406434496</v>
+      </c>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n">
+        <v>6.821</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>1.545</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Peer median</t>
+        </is>
+      </c>
+      <c r="D14" s="35">
+        <f>MEDIAN(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="E14" s="35">
+        <f>MEDIAN(E6:E12)</f>
+        <v/>
+      </c>
+      <c r="F14" s="35">
+        <f>MEDIAN(F6:F12)</f>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D15" s="34">
-        <f>MEDIAN(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E15" s="34">
-        <f>MEDIAN(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F15" s="34">
-        <f>MEDIAN(F6:F13)</f>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="D15" s="35">
+        <f>AVERAGE(D6:D12)</f>
+        <v/>
+      </c>
+      <c r="E15" s="35">
+        <f>AVERAGE(E6:E12)</f>
+        <v/>
+      </c>
+      <c r="F15" s="35">
+        <f>AVERAGE(F6:F12)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Peer mean</t>
-        </is>
-      </c>
-      <c r="D16" s="34">
-        <f>AVERAGE(D6:D13)</f>
-        <v/>
-      </c>
-      <c r="E16" s="34">
-        <f>AVERAGE(E6:E13)</f>
-        <v/>
-      </c>
-      <c r="F16" s="34">
-        <f>AVERAGE(F6:F13)</f>
-        <v/>
+          <t>Target percentile vs peers</t>
+        </is>
+      </c>
+      <c r="D16" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="36" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F16" s="36" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Target percentile vs peers</t>
-        </is>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F17" s="35" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.822</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>268.14</v>
+        <v>267.75</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>116.03</v>
+        <v>126.54</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.311</v>
+        <v>1.116</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.777</v>
+        <v>0.742</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04654000282287598</v>
+        <v>0.04659999847412109</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>42276819.16745669</v>
+        <v>42276819.97787261</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>116.03</v>
+        <v>126.54</v>
       </c>
     </row>
     <row r="38">
@@ -1446,7 +1446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>4905379328</v>
+        <v>5349708800</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>13.05</v>
+        <v>14.23</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>9.9</v>
+        <v>10.74</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7414156288</v>
+        <v>7917784576</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>34.899616</v>
+        <v>24.072317</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>13.508</v>
+        <v>12.019</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.414</v>
+        <v>0.407</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1451626624</v>
+        <v>1569392000</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>5.257</v>
+        <v>5.349</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.67</v>
+        <v>0.6820000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>4209519872</v>
+        <v>4238946560</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>22.351564</v>
+        <v>22.507812</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>15.191</v>
+        <v>14.73</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.912</v>
+        <v>2.823</v>
       </c>
     </row>
     <row r="9">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>6858031616</v>
+        <v>6550797824</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>19.578947</v>
+        <v>15.519125</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>8.012</v>
+        <v>7.86</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.179</v>
+        <v>0.178</v>
       </c>
     </row>
     <row r="10">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>3140250880</v>
+        <v>3447192576</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>3649148672</v>
+        <v>4857491968</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>50.894737</v>
+        <v>58.439392</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>36.563</v>
+        <v>41.486</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>2.652</v>
+        <v>3.301</v>
       </c>
     </row>
     <row r="12">
@@ -1680,72 +1680,94 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>406434496</v>
+        <v>378270912</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>6.821</v>
+        <v>6.716</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.545</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Peer median</t>
-        </is>
-      </c>
-      <c r="D14" s="35">
-        <f>MEDIAN(D6:D12)</f>
-        <v/>
-      </c>
-      <c r="E14" s="35">
-        <f>MEDIAN(E6:E12)</f>
-        <v/>
-      </c>
-      <c r="F14" s="35">
-        <f>MEDIAN(F6:F12)</f>
-        <v/>
+        <v>1.521</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SLAB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Silicon Laboratories, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="33" t="n">
+        <v>7229945856</v>
+      </c>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n">
+        <v>-326.479</v>
+      </c>
+      <c r="F13" s="34" t="n">
+        <v>8.276</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Peer mean</t>
+          <t>Peer median</t>
         </is>
       </c>
       <c r="D15" s="35">
-        <f>AVERAGE(D6:D12)</f>
+        <f>MEDIAN(D6:D13)</f>
         <v/>
       </c>
       <c r="E15" s="35">
-        <f>AVERAGE(E6:E12)</f>
+        <f>MEDIAN(E6:E13)</f>
         <v/>
       </c>
       <c r="F15" s="35">
-        <f>AVERAGE(F6:F12)</f>
+        <f>MEDIAN(F6:F13)</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>Peer mean</t>
+        </is>
+      </c>
+      <c r="D16" s="35">
+        <f>AVERAGE(D6:D13)</f>
+        <v/>
+      </c>
+      <c r="E16" s="35">
+        <f>AVERAGE(E6:E13)</f>
+        <v/>
+      </c>
+      <c r="F16" s="35">
+        <f>AVERAGE(F6:F13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
           <t>Target percentile vs peers</t>
         </is>
       </c>
-      <c r="D16" s="36" t="n">
+      <c r="D17" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="36" t="n">
+      <c r="E17" s="36" t="n">
         <v>0.4</v>
       </c>
-      <c r="F16" s="36" t="n">
+      <c r="F17" s="36" t="n">
         <v>0.6</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>(higher pct = more expensive than peers)</t>
         </is>

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-08 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>267.75</v>
+        <v>265.19</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>126.54</v>
+        <v>126.895</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.116</v>
+        <v>1.09</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.742</v>
+        <v>0.741</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04659999847412109</v>
+        <v>0.04699999809265137</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>42276819.97787261</v>
+        <v>42276819.85893849</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>126.54</v>
+        <v>126.895</v>
       </c>
     </row>
     <row r="38">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5349708800</v>
+        <v>5364717056</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.23</v>
+        <v>14.27</v>
       </c>
       <c r="E5" s="32" t="n">
         <v>10.74</v>
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7917784576</v>
+        <v>7989145600</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.072317</v>
+        <v>24.289276</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>12.019</v>
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1569392000</v>
+        <v>1563290240</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>4238946560</v>
+        <v>4224232960</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>22.507812</v>
+        <v>22.429688</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>14.73</v>
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>6550797824</v>
+        <v>6430853632</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>15.519125</v>
+        <v>15.234972</v>
       </c>
       <c r="E9" s="34" t="n">
         <v>7.86</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>3447192576</v>
+        <v>3450143744</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4857491968</v>
+        <v>4866308096</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>58.439392</v>
+        <v>58.545452</v>
       </c>
       <c r="E11" s="34" t="n">
         <v>41.486</v>
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>378270912</v>
+        <v>368969152</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>7229945856</v>
+        <v>7199107584</v>
       </c>
       <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-10 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-11 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>265.19</v>
+        <v>266.21</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>126.895</v>
+        <v>125.01</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.741</v>
+        <v>0.747</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04699999809265137</v>
+        <v>0.04684000015258789</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>42276819.85893849</v>
+        <v>42276820.09439245</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>126.895</v>
+        <v>125.01</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5364717056</v>
+        <v>5285025280</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.27</v>
+        <v>14.06</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.74</v>
+        <v>10.68</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7989145600</v>
+        <v>7953054720</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.289276</v>
+        <v>24.17955</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>12.019</v>
+        <v>12.095</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.407</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1563290240</v>
+        <v>1555662976</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>5.349</v>
+        <v>5.339</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.6820000000000001</v>
+        <v>0.681</v>
       </c>
     </row>
     <row r="8">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>4224232960</v>
+        <v>4130066944</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>22.429688</v>
+        <v>21.929688</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>14.73</v>
+        <v>14.686</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.823</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="9">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>6430853632</v>
+        <v>6396254720</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>15.234972</v>
+        <v>15.153005</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>7.86</v>
+        <v>7.738</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.178</v>
+        <v>0.176</v>
       </c>
     </row>
     <row r="10">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>3450143744</v>
+        <v>4883031040</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4866308096</v>
+        <v>4963281408</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>58.545452</v>
+        <v>59.71212</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>41.486</v>
+        <v>41.975</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.301</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="12">
@@ -1680,14 +1680,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>368969152</v>
+        <v>360184160</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>6.716</v>
+        <v>6.692</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.521</v>
+        <v>1.516</v>
       </c>
     </row>
     <row r="13">
@@ -1702,14 +1702,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>7199107584</v>
+        <v>7202570752</v>
       </c>
       <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n">
-        <v>-326.479</v>
+        <v>-325.242</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>8.276</v>
+        <v>8.244999999999999</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-11 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>266.21</v>
+        <v>266.85</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>125.01</v>
+        <v>129.52</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.747</v>
+        <v>0.732</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04684000015258789</v>
+        <v>0.04674000263214111</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>42276820.09439245</v>
+        <v>42276822.73008029</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>125.01</v>
+        <v>129.52</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5285025280</v>
+        <v>5475694080</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.06</v>
+        <v>14.57</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.68</v>
+        <v>10.71</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.08</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7953054720</v>
+        <v>7391902720</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>24.17955</v>
+        <v>22.460098</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>12.095</v>
+        <v>11.636</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.41</v>
+        <v>0.398</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1555662976</v>
+        <v>1530340224</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>5.339</v>
+        <v>5.251</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.681</v>
+        <v>0.669</v>
       </c>
     </row>
     <row r="8">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>4130066944</v>
+        <v>4150665728</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>21.929688</v>
+        <v>20.742645</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>14.686</v>
+        <v>12.754</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.815</v>
+        <v>2.303</v>
       </c>
     </row>
     <row r="9">
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>6396254720</v>
+        <v>6308603392</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>15.153005</v>
+        <v>14.945355</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>7.738</v>
+        <v>7.745</v>
       </c>
       <c r="F9" s="34" t="n">
         <v>0.176</v>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>4883031040</v>
+        <v>5338701312</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4963281408</v>
+        <v>4915424256</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>59.71212</v>
+        <v>59.13636</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>41.975</v>
+        <v>41.195</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.34</v>
+        <v>3.278</v>
       </c>
     </row>
     <row r="12">
@@ -1680,14 +1680,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>360184160</v>
+        <v>349843648</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>6.692</v>
+        <v>6.889</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.516</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="13">
@@ -1702,14 +1702,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>7202570752</v>
+        <v>7303650304</v>
       </c>
       <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n">
-        <v>-325.242</v>
+        <v>-692.5309999999999</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>8.244999999999999</v>
+        <v>8.074</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-19 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>266.85</v>
+        <v>263.04</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>129.52</v>
+        <v>128.39</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.06</v>
+        <v>1.049</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.732</v>
+        <v>0.736</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04674000263214111</v>
+        <v>0.04734000205993652</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>42276822.73008029</v>
+        <v>42276819.81462731</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>129.52</v>
+        <v>128.39</v>
       </c>
     </row>
     <row r="38">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5475694080</v>
+        <v>5427920896</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.57</v>
+        <v>14.44</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.71</v>
+        <v>10.73</v>
       </c>
       <c r="F5" s="32" t="n">
         <v>1.08</v>
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7391902720</v>
+        <v>7143631872</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>22.460098</v>
+        <v>21.705734</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.636</v>
+        <v>11.07</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.398</v>
+        <v>0.378</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1530340224</v>
+        <v>1550781440</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>5.251</v>
+        <v>5.324</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.669</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="8">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>4150665728</v>
+        <v>4365482496</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>20.742645</v>
+        <v>21.816175</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>12.754</v>
+        <v>13.578</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.303</v>
+        <v>2.452</v>
       </c>
     </row>
     <row r="9">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>6308603392</v>
+        <v>6403174400</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>14.945355</v>
+        <v>15.169398</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>7.745</v>
+        <v>7.656</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.176</v>
+        <v>0.174</v>
       </c>
     </row>
     <row r="10">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>5338701312</v>
+        <v>5492078592</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>4915424256</v>
+        <v>5073906688</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>59.13636</v>
+        <v>61.043026</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>41.195</v>
+        <v>41.312</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.278</v>
+        <v>3.287</v>
       </c>
     </row>
     <row r="12">
@@ -1680,14 +1680,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>349843648</v>
+        <v>357414880</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>6.889</v>
+        <v>6.898</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.51</v>
+        <v>1.512</v>
       </c>
     </row>
     <row r="13">
@@ -1702,14 +1702,14 @@
         </is>
       </c>
       <c r="C13" s="33" t="n">
-        <v>7303650304</v>
+        <v>7273953792</v>
       </c>
       <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n">
-        <v>-692.5309999999999</v>
+        <v>-689.522</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>8.074</v>
+        <v>8.038</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-21 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>263.04</v>
+        <v>262.79</v>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>128.39</v>
+        <v>128.04</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>1.049</v>
+        <v>1.052</v>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.736</v>
+        <v>0.737</v>
       </c>
       <c r="C13" s="2" t="inlineStr"/>
     </row>
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.04734000205993652</v>
+        <v>0.0473799991607666</v>
       </c>
     </row>
     <row r="6">
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B35" s="21" t="n">
-        <v>42276819.81462731</v>
+        <v>42276816.49484536</v>
       </c>
     </row>
     <row r="36">
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="B37" s="23" t="n">
-        <v>128.39</v>
+        <v>128.04</v>
       </c>
     </row>
     <row r="38">
@@ -1520,16 +1520,16 @@
         </is>
       </c>
       <c r="C5" s="31" t="n">
-        <v>5427920896</v>
+        <v>5413123584</v>
       </c>
       <c r="D5" s="32" t="n">
-        <v>14.44</v>
+        <v>14.4</v>
       </c>
       <c r="E5" s="32" t="n">
-        <v>10.73</v>
+        <v>10.83</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="6">
@@ -1544,16 +1544,16 @@
         </is>
       </c>
       <c r="C6" s="33" t="n">
-        <v>7143631872</v>
+        <v>7274948608</v>
       </c>
       <c r="D6" s="34" t="n">
-        <v>21.705734</v>
+        <v>22.104736</v>
       </c>
       <c r="E6" s="34" t="n">
-        <v>11.07</v>
+        <v>11.222</v>
       </c>
       <c r="F6" s="34" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
     </row>
     <row r="7">
@@ -1568,14 +1568,14 @@
         </is>
       </c>
       <c r="C7" s="33" t="n">
-        <v>1550781440</v>
+        <v>1549866112</v>
       </c>
       <c r="D7" s="34" t="n"/>
       <c r="E7" s="34" t="n">
-        <v>5.324</v>
+        <v>5.334</v>
       </c>
       <c r="F7" s="34" t="n">
-        <v>0.679</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="8">
@@ -1590,16 +1590,16 @@
         </is>
       </c>
       <c r="C8" s="33" t="n">
-        <v>4365482496</v>
+        <v>4464062464</v>
       </c>
       <c r="D8" s="34" t="n">
-        <v>21.816175</v>
+        <v>22.308823</v>
       </c>
       <c r="E8" s="34" t="n">
-        <v>13.578</v>
+        <v>14.555</v>
       </c>
       <c r="F8" s="34" t="n">
-        <v>2.452</v>
+        <v>2.628</v>
       </c>
     </row>
     <row r="9">
@@ -1614,16 +1614,16 @@
         </is>
       </c>
       <c r="C9" s="33" t="n">
-        <v>6403174400</v>
+        <v>6343202304</v>
       </c>
       <c r="D9" s="34" t="n">
-        <v>15.169398</v>
+        <v>15.027322</v>
       </c>
       <c r="E9" s="34" t="n">
-        <v>7.656</v>
+        <v>7.696</v>
       </c>
       <c r="F9" s="34" t="n">
-        <v>0.174</v>
+        <v>0.175</v>
       </c>
     </row>
     <row r="10">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="C10" s="33" t="n">
-        <v>5492078592</v>
+        <v>5539271680</v>
       </c>
       <c r="D10" s="34" t="n"/>
       <c r="E10" s="34" t="n"/>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="C11" s="33" t="n">
-        <v>5073906688</v>
+        <v>5037585920</v>
       </c>
       <c r="D11" s="34" t="n">
-        <v>61.043026</v>
+        <v>60.60606</v>
       </c>
       <c r="E11" s="34" t="n">
-        <v>41.312</v>
+        <v>43.15</v>
       </c>
       <c r="F11" s="34" t="n">
-        <v>3.287</v>
+        <v>3.433</v>
       </c>
     </row>
     <row r="12">
@@ -1680,14 +1680,14 @@
         </is>
       </c>
       <c r="C12" s="33" t="n">
-        <v>357414880</v>
+        <v>358720288</v>
       </c>
       <c r="D12" s="34" t="n"/>
       <c r="E12" s="34" t="n">
-        <v>6.898</v>
+        <v>6.936</v>
       </c>
       <c r="F12" s="34" t="n">
-        <v>1.512</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="13">
@@ -1706,10 +1706,10 @@
       </c>
       <c r="D13" s="34" t="n"/>
       <c r="E13" s="34" t="n">
-        <v>-689.522</v>
+        <v>-689.187</v>
       </c>
       <c r="F13" s="34" t="n">
-        <v>8.038</v>
+        <v>8.035</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/SAIC_research.xlsx
+++ b/app/reports/SAIC_research.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-22 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-23 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
